--- a/education_forms/041_study_notes_collection_form--education_forms.xlsx
+++ b/education_forms/041_study_notes_collection_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Study Tags</t>
+          <t>Study Notes Tags Tag</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Study Tags (Education)</t>
+          <t>Study Notes Tags Tag Education</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Study Tags (Subject)</t>
+          <t>Study Notes Tags Tag Subject</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Study Tags (Lesson)</t>
+          <t>Study Notes Tags Tag Lesson</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Study Tags (Level)</t>
+          <t>Study Notes Tags Tag Level</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>study_notes_tags_tag_education</t>
+          <t>study_notes_tags_tag_education_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Study Tags (Education)</t>
+          <t>Study Notes Tags Tag Education 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>study_notes_tags_tag_subject</t>
+          <t>study_notes_tags_tag_subject_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Study Tags (Subject)</t>
+          <t>Study Notes Tags Tag Subject 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>study_notes_tags_tag_lesson</t>
+          <t>study_notes_tags_tag_lesson_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Study Tags (Lesson)</t>
+          <t>Study Notes Tags Tag Lesson 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>study_notes_tags_tag</t>
+          <t>study_notes_tags_tag_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Study Tags</t>
+          <t>Study Notes Tags Tag 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1199,46 +1199,46 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>study_notes_category_choices</t>
+          <t>study_notes_educator_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>study_notes_category_choices</t>
+          <t>study_notes_educator_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option 5</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1250,571 +1250,520 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>study_notes_educator_choices</t>
+          <t>study_notes_student_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>study_notes_educator_choices</t>
+          <t>study_notes_student_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>study_notes_educator_choices</t>
+          <t>study_notes_tags_education_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>study_notes_student_choices</t>
+          <t>study_notes_tags_education_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>study_notes_student_choices</t>
+          <t>study_notes_tags_subject_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>study_notes_tags_education_choices</t>
+          <t>study_notes_tags_subject_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>study_notes_tags_education_choices</t>
+          <t>study_notes_tags_level_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>study_notes_tags_subject_choices</t>
+          <t>study_notes_tags_level_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>study_notes_tags_subject_choices</t>
+          <t>study_notes_tags_lesson_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>study_notes_tags_level_choices</t>
+          <t>study_notes_tags_lesson_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>study_notes_tags_level_choices</t>
+          <t>study_notes_tags_tag_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>study_notes_tags_lesson_choices</t>
+          <t>study_notes_tags_tag_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>study_notes_tags_lesson_choices</t>
+          <t>study_notes_tags_tag_education_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>study_notes_tags_tag_choices</t>
+          <t>study_notes_tags_tag_education_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>study_notes_tags_tag_choices</t>
+          <t>study_notes_tags_tag_subject_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>study_notes_tags_tag_education_choices</t>
+          <t>study_notes_tags_tag_subject_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>study_notes_tags_tag_education_choices</t>
+          <t>study_notes_tags_tag_lesson_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>study_notes_tags_tag_subject_choices</t>
+          <t>study_notes_tags_tag_lesson_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>study_notes_tags_tag_subject_choices</t>
+          <t>study_notes_tags_tag_category_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>study_notes_tags_tag_lesson_choices</t>
+          <t>study_notes_tags_tag_category_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>study_notes_tags_tag_lesson_choices</t>
+          <t>study_notes_tags_tag_level_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>study_notes_tags_tag_category_choices</t>
+          <t>study_notes_tags_tag_level_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>study_notes_tags_tag_category_choices</t>
+          <t>study_notes_tags_tag_education_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>study_notes_tags_tag_level_choices</t>
+          <t>study_notes_tags_tag_education_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>study_notes_tags_tag_level_choices</t>
+          <t>study_notes_tags_tag_subject_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>study_notes_tags_tag_education_choices</t>
+          <t>study_notes_tags_tag_subject_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>study_notes_tags_tag_education_choices</t>
+          <t>study_notes_tags_tag_lesson_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>study_notes_tags_tag_subject_choices</t>
+          <t>study_notes_tags_tag_lesson_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>study_notes_tags_tag_subject_choices</t>
+          <t>study_notes_tags_tag_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>study_notes_tags_tag_lesson_choices</t>
+          <t>study_notes_tags_tag_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>study_notes_tags_tag_lesson_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>study_notes_tags_tag_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>study_notes_tags_tag_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
         <is>
           <t>No</t>
         </is>
